--- a/testdata/05-users.xlsx
+++ b/testdata/05-users.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t>name</t>
   </si>
@@ -40,6 +40,9 @@
     <t>categories</t>
   </si>
   <si>
+    <t>sub_categories</t>
+  </si>
+  <si>
     <t>password</t>
   </si>
   <si>
@@ -310,10 +313,46 @@
     <t>P08</t>
   </si>
   <si>
+    <t>Divya Menon</t>
+  </si>
+  <si>
+    <t>SS1020</t>
+  </si>
+  <si>
+    <t>divya.menon@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>whl1</t>
+  </si>
+  <si>
+    <t>Linen</t>
+  </si>
+  <si>
+    <t>Harish Bhat</t>
+  </si>
+  <si>
+    <t>SS1021</t>
+  </si>
+  <si>
+    <t>harish.bhat@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>Tarun Khanna</t>
+  </si>
+  <si>
+    <t>SS1022</t>
+  </si>
+  <si>
+    <t>tarun.khanna@test.saltstayz.com</t>
+  </si>
+  <si>
+    <t>whl2</t>
+  </si>
+  <si>
     <t>Karan Kapoor</t>
   </si>
   <si>
-    <t>SS1020</t>
+    <t>SS1023</t>
   </si>
   <si>
     <t>karan.kapoor@test.saltstayz.com</t>
@@ -331,7 +370,7 @@
     <t>Nisha Pillai</t>
   </si>
   <si>
-    <t>SS1021</t>
+    <t>SS1024</t>
   </si>
   <si>
     <t>nisha.pillai@test.saltstayz.com</t>
@@ -343,7 +382,7 @@
     <t>Anjali Rao</t>
   </si>
   <si>
-    <t>SS1022</t>
+    <t>SS1025</t>
   </si>
   <si>
     <t>anjali.rao@test.saltstayz.com</t>
@@ -358,7 +397,7 @@
     <t>Meera Kapoor</t>
   </si>
   <si>
-    <t>SS1023</t>
+    <t>SS1026</t>
   </si>
   <si>
     <t>meera.kapoor@test.saltstayz.com</t>
@@ -376,7 +415,7 @@
     <t>Rakesh Jain</t>
   </si>
   <si>
-    <t>SS1024</t>
+    <t>SS1027</t>
   </si>
   <si>
     <t>rakesh.jain@test.saltstayz.com</t>
@@ -388,7 +427,7 @@
     <t>Vivek Nair</t>
   </si>
   <si>
-    <t>SS1025</t>
+    <t>SS1028</t>
   </si>
   <si>
     <t>vivek.nair@test.saltstayz.com</t>
@@ -400,7 +439,7 @@
     <t>Anil Sethi</t>
   </si>
   <si>
-    <t>SS1026</t>
+    <t>SS1029</t>
   </si>
   <si>
     <t>anil.sethi@test.saltstayz.com</t>
@@ -412,7 +451,7 @@
     <t>Sana Qureshi</t>
   </si>
   <si>
-    <t>SS1027</t>
+    <t>SS1030</t>
   </si>
   <si>
     <t>sana.qureshi@test.saltstayz.com</t>
@@ -421,7 +460,7 @@
     <t>Gaurav Tiwari</t>
   </si>
   <si>
-    <t>SS1028</t>
+    <t>SS1031</t>
   </si>
   <si>
     <t>gaurav.tiwari@test.saltstayz.com</t>
@@ -755,7 +794,8 @@
     <col customWidth="true" max="6" min="6" style="2" width="10"/>
     <col customWidth="true" max="7" min="7" style="2" width="39"/>
     <col customWidth="true" max="8" min="8" style="2" width="17"/>
-    <col customWidth="true" max="9" min="9" style="2" width="11"/>
+    <col customWidth="true" max="9" min="9" style="2" width="16"/>
+    <col customWidth="true" max="10" min="10" style="2" width="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,534 +826,558 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>15</v>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>15</v>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>15</v>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>15</v>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>15</v>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>15</v>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>15</v>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
-        <v>15</v>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>15</v>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="I13" s="2" t="s">
-        <v>15</v>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
-        <v>15</v>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2"/>
-      <c r="I15" s="2" t="s">
-        <v>15</v>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>15</v>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2"/>
-      <c r="I17" s="2" t="s">
-        <v>15</v>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
-        <v>15</v>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H19" s="2"/>
-      <c r="I19" s="2" t="s">
-        <v>15</v>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>15</v>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H21" s="2"/>
-      <c r="I21" s="2" t="s">
-        <v>15</v>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>102</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>15</v>
+      <c r="J22" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1328,192 +1392,280 @@
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2"/>
-      <c r="I23" s="2" t="s">
-        <v>15</v>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2"/>
-      <c r="I24" s="2" t="s">
-        <v>15</v>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="s">
-        <v>15</v>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="H26" s="2"/>
-      <c r="I26" s="2" t="s">
-        <v>15</v>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="H27" s="2"/>
-      <c r="I27" s="2" t="s">
-        <v>15</v>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>130</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H28" s="2"/>
-      <c r="I28" s="2" t="s">
-        <v>15</v>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="H29" s="2"/>
-      <c r="I29" s="2" t="s">
-        <v>15</v>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2" t="s">
-        <v>15</v>
+      <c r="F33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
